--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,28 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-2.0.0-us-wipF\InputData\elec\MPCbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiyang.zhang\Desktop\eps-us-3.4.7 working_0117_wing_endofday\eps-us-3.4.7 HK working\InputData\elec\MPCbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{ACF651EF-F2FB-4325-ABB0-8A871EFFF361}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{F4293027-9FC4-40B8-9371-3B529C7D8CD1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D8B4D1-DF9C-4A67-BA6A-A9FD36871897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="MPCbS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -449,9 +454,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -489,9 +494,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -524,26 +529,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -576,26 +564,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -770,9 +741,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="60.85546875" customWidth="1"/>
+    <col min="2" max="2" width="60.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -941,13 +912,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.7265625" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" customWidth="1"/>
     <col min="4" max="4" width="71" customWidth="1"/>
-    <col min="5" max="5" width="22.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1072,7 +1043,7 @@
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:19" ht="45">
+    <row r="12" spans="1:19" ht="43.5">
       <c r="E12" s="21" t="s">
         <v>29</v>
       </c>
@@ -1080,7 +1051,7 @@
         <v>1.714</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="45">
+    <row r="13" spans="1:19" ht="43.5">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="D13" s="6"/>
@@ -1091,7 +1062,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="60">
+    <row r="14" spans="1:19" ht="58">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="D14" s="1"/>
@@ -1168,10 +1139,10 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1325,24 +1296,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1576,10 +1529,40 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7D45668-82EE-4795-8390-B5A7CC99D20D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4B95FC-9B95-4C8A-8D30-A1811A2B72B8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
+    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1603,21 +1586,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA4B95FC-9B95-4C8A-8D30-A1811A2B72B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7D45668-82EE-4795-8390-B5A7CC99D20D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>